--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R3" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,9 +847,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,19 +958,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>78700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,9 +1160,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>78700</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R7" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,19 +1271,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,27 +1423,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1451,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R9" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,17 +1488,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,26 +1524,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1556,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R10" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,13 +1590,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139273</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>78791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466112</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858564</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,19 +1801,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129138903</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>78791</v>
+        <v>79624</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465965</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858521</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,9 +2018,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,7 +2058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B15" t="n">
         <v>78792</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R15" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,19 +2129,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B16" t="n">
         <v>78792</v>
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R16" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,9 +2230,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,27 +2483,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2511,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R19" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,32 +2543,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2588,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,26 +2584,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R20" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,13 +2660,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R21" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,9 +2760,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129138728</v>
+        <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>91541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,35 +3033,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3069,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466017</v>
+        <v>466047</v>
       </c>
       <c r="R24" t="n">
-        <v>6858509</v>
+        <v>6858491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,17 +3093,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3131,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139379</v>
+        <v>129138728</v>
       </c>
       <c r="B25" t="n">
-        <v>91538</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,26 +3144,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3169,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466047</v>
+        <v>466017</v>
       </c>
       <c r="R25" t="n">
-        <v>6858491</v>
+        <v>6858509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,28 +3213,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139294</v>
+        <v>129139190</v>
       </c>
       <c r="B26" t="n">
-        <v>83010</v>
+        <v>78792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466066</v>
+        <v>466251</v>
       </c>
       <c r="R26" t="n">
-        <v>6858495</v>
+        <v>6858668</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138795</v>
+        <v>129139294</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>83010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466160</v>
+        <v>466066</v>
       </c>
       <c r="R27" t="n">
-        <v>6858585</v>
+        <v>6858495</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,9 +3424,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139190</v>
+        <v>129138795</v>
       </c>
       <c r="B28" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466251</v>
+        <v>466160</v>
       </c>
       <c r="R28" t="n">
-        <v>6858668</v>
+        <v>6858585</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,19 +3535,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>79653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,27 +3778,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3806,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R31" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,17 +3853,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3984,10 +3979,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139271</v>
+        <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,26 +3990,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4022,10 +4018,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466112</v>
+        <v>466352</v>
       </c>
       <c r="R33" t="n">
-        <v>6858564</v>
+        <v>6858689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4070,13 +4066,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129139440</v>
+        <v>129138758</v>
       </c>
       <c r="B39" t="n">
-        <v>78700</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4641,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466175</v>
+        <v>465994</v>
       </c>
       <c r="R39" t="n">
-        <v>6858646</v>
+        <v>6858533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,19 +4701,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>78700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,9 +4802,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4839,6 +4839,577 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129175846</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79624</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>466288</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6858746</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129175788</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>466189</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6858646</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129175770</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>466134</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6858579</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129175800</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79624</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>466330</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6858715</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129175796</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79624</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>466166</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6858663</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129138835</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129138897</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B6" t="n">
-        <v>78700</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R6" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,19 +1160,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>78701</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R7" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,9 +1261,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>129139390</v>
       </c>
       <c r="B8" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129139273</v>
       </c>
       <c r="B11" t="n">
-        <v>83010</v>
+        <v>79625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>466112</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>83011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,9 +1801,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1852,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,32 +1912,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B14" t="n">
-        <v>79624</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,26 +1953,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,13 +2029,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R15" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,9 +2129,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B16" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R16" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,19 +2240,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,7 +2273,7 @@
         <v>129138762</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>129138892</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129139174</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139379</v>
+        <v>129138795</v>
       </c>
       <c r="B24" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466047</v>
+        <v>466160</v>
       </c>
       <c r="R24" t="n">
-        <v>6858491</v>
+        <v>6858585</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,19 +3093,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138728</v>
+        <v>129138780</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,35 +3134,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3180,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466017</v>
+        <v>466057</v>
       </c>
       <c r="R25" t="n">
-        <v>6858509</v>
+        <v>6858545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,6 +3205,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3242,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B26" t="n">
-        <v>78792</v>
+        <v>91544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3280,10 +3262,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R26" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3356,7 +3338,7 @@
         <v>129139294</v>
       </c>
       <c r="B27" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138795</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,26 +3457,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3502,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466160</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858585</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3537,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138780</v>
+        <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3576,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466057</v>
+        <v>466251</v>
       </c>
       <c r="R29" t="n">
-        <v>6858545</v>
+        <v>6858668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,9 +3626,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,7 +3669,7 @@
         <v>129138773</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>129138822</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129139434</v>
       </c>
       <c r="B34" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129138812</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139263</v>
+        <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>79653</v>
+        <v>78701</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465939</v>
+        <v>466175</v>
       </c>
       <c r="R36" t="n">
-        <v>6858553</v>
+        <v>6858646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138933</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>78042</v>
+        <v>79654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465973</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858506</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B38" t="n">
-        <v>78791</v>
+        <v>78043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R38" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,9 +4600,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4630,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138758</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465994</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858533</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129139440</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78700</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4742,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466175</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858646</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,19 +4812,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,7 +4845,7 @@
         <v>129175846</v>
       </c>
       <c r="B41" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5072,44 +5072,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B43" t="n">
-        <v>92816</v>
+        <v>79625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5118,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R43" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5191,36 +5183,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B44" t="n">
-        <v>79624</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R44" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,7 +5305,7 @@
         <v>129175796</v>
       </c>
       <c r="B45" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5411,6 +5411,228 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129197630</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>466314</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6858740</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129197620</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>466329</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6858717</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R3" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,19 +847,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R4" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,9 +948,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,26 +1423,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1450,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R9" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,13 +1489,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,27 +1529,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1552,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R10" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,17 +1594,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B15" t="n">
         <v>78793</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R15" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,19 +2129,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B16" t="n">
         <v>78793</v>
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R16" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,9 +2230,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129138795</v>
+        <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466160</v>
+        <v>466047</v>
       </c>
       <c r="R24" t="n">
-        <v>6858585</v>
+        <v>6858491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,9 +3093,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138780</v>
+        <v>129138728</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,26 +3144,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3161,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466057</v>
+        <v>466017</v>
       </c>
       <c r="R25" t="n">
-        <v>6858545</v>
+        <v>6858509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,7 +3224,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3224,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B26" t="n">
-        <v>91544</v>
+        <v>78793</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,21 +3253,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3262,10 +3280,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R26" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3446,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129138795</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,35 +3475,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3493,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466160</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858585</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,6 +3546,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3555,10 +3565,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139190</v>
+        <v>129138780</v>
       </c>
       <c r="B29" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3576,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3593,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466251</v>
+        <v>466057</v>
       </c>
       <c r="R29" t="n">
-        <v>6858668</v>
+        <v>6858545</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,19 +3636,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139271</v>
+        <v>129139365</v>
       </c>
       <c r="B31" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,26 +3778,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3805,10 +3806,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466112</v>
+        <v>466352</v>
       </c>
       <c r="R31" t="n">
-        <v>6858564</v>
+        <v>6858689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,13 +3854,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3878,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R32" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,9 +3954,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3979,10 +3994,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139365</v>
+        <v>129138822</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,27 +4005,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4018,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466352</v>
+        <v>466193</v>
       </c>
       <c r="R33" t="n">
-        <v>6858689</v>
+        <v>6858649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4051,32 +4065,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138933</v>
+        <v>129138827</v>
       </c>
       <c r="B38" t="n">
-        <v>78043</v>
+        <v>78792</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465973</v>
+        <v>465992</v>
       </c>
       <c r="R38" t="n">
-        <v>6858506</v>
+        <v>6858551</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,19 +4600,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129138758</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4641,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4678,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465994</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129138933</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>78043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>465973</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,9 +4802,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5072,36 +5072,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>79625</v>
+        <v>92819</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5110,10 +5118,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R43" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5183,44 +5191,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>79625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R44" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B12" t="n">
-        <v>83011</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,26 +1741,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1768,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R12" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,13 +1817,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129138903</v>
+        <v>129139302</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>83011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465965</v>
+        <v>466064</v>
       </c>
       <c r="R13" t="n">
-        <v>6858521</v>
+        <v>6858495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,9 +1917,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,27 +1968,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R14" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,32 +2028,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R19" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,9 +2543,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,27 +2594,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2612,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,32 +2654,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2689,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B21" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,26 +2695,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2727,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R21" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,13 +2771,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R3" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,9 +847,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,19 +958,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>78701</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,9 +1160,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>78701</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R7" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,19 +1271,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139273</v>
+        <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>79625</v>
+        <v>83011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466112</v>
+        <v>466064</v>
       </c>
       <c r="R11" t="n">
-        <v>6858564</v>
+        <v>6858495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,27 +1741,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1769,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,32 +1801,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1846,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>83011</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1884,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,13 +1918,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129138903</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465965</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858521</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,9 +2018,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,7 +2058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B15" t="n">
         <v>78793</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R15" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,9 +2129,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B16" t="n">
         <v>78793</v>
@@ -2197,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R16" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,19 +2240,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B19" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,26 +2483,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2510,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R19" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,13 +2559,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2583,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R20" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,9 +2659,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,27 +2710,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2723,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R21" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,32 +2770,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138728</v>
+        <v>129138795</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,35 +3144,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3180,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466017</v>
+        <v>466160</v>
       </c>
       <c r="R25" t="n">
-        <v>6858509</v>
+        <v>6858585</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,6 +3215,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3242,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139190</v>
+        <v>129138780</v>
       </c>
       <c r="B26" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,21 +3245,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3280,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466251</v>
+        <v>466057</v>
       </c>
       <c r="R26" t="n">
-        <v>6858668</v>
+        <v>6858545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,19 +3305,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138795</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,26 +3457,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3502,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466160</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858585</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3537,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138780</v>
+        <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3576,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466057</v>
+        <v>466251</v>
       </c>
       <c r="R29" t="n">
-        <v>6858545</v>
+        <v>6858668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,9 +3626,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,27 +3778,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3806,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R31" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,17 +3853,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3883,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,21 +3889,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R32" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,19 +3949,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3994,10 +3979,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4005,26 +3990,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4032,10 +4018,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R33" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,18 +4051,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138933</v>
       </c>
       <c r="B37" t="n">
-        <v>79654</v>
+        <v>78043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465973</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858506</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138827</v>
+        <v>129138758</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465992</v>
+        <v>465994</v>
       </c>
       <c r="R38" t="n">
-        <v>6858551</v>
+        <v>6858533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138758</v>
+        <v>129139263</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4641,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465994</v>
+        <v>465939</v>
       </c>
       <c r="R39" t="n">
-        <v>6858533</v>
+        <v>6858553</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,9 +4701,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138933</v>
+        <v>129138827</v>
       </c>
       <c r="B40" t="n">
-        <v>78043</v>
+        <v>78792</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4742,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465973</v>
+        <v>465992</v>
       </c>
       <c r="R40" t="n">
-        <v>6858506</v>
+        <v>6858551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,19 +4812,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129138835</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129138897</v>
       </c>
       <c r="B5" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129139390</v>
       </c>
       <c r="B8" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,27 +1423,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1451,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R9" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,17 +1488,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,26 +1524,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1556,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R10" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,13 +1590,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B11" t="n">
-        <v>83011</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,26 +1630,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,13 +1706,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>83015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,9 +1806,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>78796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1857,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,32 +1917,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>129139202</v>
       </c>
       <c r="B15" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129138924</v>
       </c>
       <c r="B16" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>129138762</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>129138892</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,27 +2483,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2511,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R19" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,32 +2543,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2588,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B20" t="n">
-        <v>78793</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,26 +2584,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R20" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,13 +2660,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R21" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,9 +2760,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129139174</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139379</v>
+        <v>129138795</v>
       </c>
       <c r="B24" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466047</v>
+        <v>466160</v>
       </c>
       <c r="R24" t="n">
-        <v>6858491</v>
+        <v>6858585</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,19 +3093,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138795</v>
+        <v>129139294</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>83015</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466160</v>
+        <v>466066</v>
       </c>
       <c r="R25" t="n">
-        <v>6858585</v>
+        <v>6858495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,9 +3194,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3237,7 +3237,7 @@
         <v>129138780</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139294</v>
+        <v>129139379</v>
       </c>
       <c r="B27" t="n">
-        <v>83011</v>
+        <v>91551</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466066</v>
+        <v>466047</v>
       </c>
       <c r="R27" t="n">
-        <v>6858495</v>
+        <v>6858491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129139190</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>78797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,35 +3457,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3493,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466251</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3526,17 +3517,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3555,10 +3557,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139190</v>
+        <v>129138728</v>
       </c>
       <c r="B29" t="n">
-        <v>78793</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,26 +3568,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3593,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466251</v>
+        <v>466017</v>
       </c>
       <c r="R29" t="n">
-        <v>6858668</v>
+        <v>6858509</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,28 +3637,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>129138773</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,19 +3838,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,21 +3879,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3916,10 +3906,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R32" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,9 +3939,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,7 +3982,7 @@
         <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129139434</v>
       </c>
       <c r="B34" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129138812</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>129138933</v>
       </c>
       <c r="B37" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138758</v>
+        <v>129139263</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465994</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>6858533</v>
+        <v>6858553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,9 +4600,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4630,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,19 +4711,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138827</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465992</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858551</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
         <v>129175846</v>
       </c>
       <c r="B41" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>129175796</v>
       </c>
       <c r="B45" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>129197630</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>129197620</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5633,6 +5633,808 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129281326</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>466342</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6858743</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129281312</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>466110</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6858566</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129281320</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>466268</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6858643</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129281308</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>466059</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6858509</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129281353</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90562</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>466390</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6858754</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129281315</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>466103</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6858666</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129281346</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>864</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>466062</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6858497</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139440</v>
+        <v>129139263</v>
       </c>
       <c r="B36" t="n">
-        <v>78705</v>
+        <v>79658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466175</v>
+        <v>465939</v>
       </c>
       <c r="R36" t="n">
-        <v>6858646</v>
+        <v>6858553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138933</v>
+        <v>129138827</v>
       </c>
       <c r="B37" t="n">
-        <v>78047</v>
+        <v>78796</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465973</v>
+        <v>465992</v>
       </c>
       <c r="R37" t="n">
-        <v>6858506</v>
+        <v>6858551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,19 +4489,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4529,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129139263</v>
+        <v>129138758</v>
       </c>
       <c r="B38" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,21 +4530,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465939</v>
+        <v>465994</v>
       </c>
       <c r="R38" t="n">
-        <v>6858553</v>
+        <v>6858533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,19 +4590,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4620,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B39" t="n">
-        <v>78796</v>
+        <v>78047</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4631,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4678,10 +4658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,9 +4691,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>78705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,9 +4802,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5072,44 +5072,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B43" t="n">
-        <v>92826</v>
+        <v>79629</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5118,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R43" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5191,36 +5183,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B44" t="n">
-        <v>79629</v>
+        <v>92826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R44" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R3" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,19 +847,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R4" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,9 +948,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,26 +1423,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1450,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R9" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,13 +1489,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,27 +1529,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1552,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R10" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,17 +1594,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>83005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,27 +1630,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1658,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R11" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,17 +1705,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>83015</v>
+        <v>78796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,19 +1801,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129138903</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>78796</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1884,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465965</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858521</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,18 +1903,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B15" t="n">
         <v>78797</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R15" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,19 +2129,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B16" t="n">
         <v>78797</v>
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R16" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,9 +2230,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129138795</v>
+        <v>129139294</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>83005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466160</v>
+        <v>466066</v>
       </c>
       <c r="R24" t="n">
-        <v>6858585</v>
+        <v>6858495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,9 +3093,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139294</v>
+        <v>129138780</v>
       </c>
       <c r="B25" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466066</v>
+        <v>466057</v>
       </c>
       <c r="R25" t="n">
-        <v>6858495</v>
+        <v>6858545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,19 +3204,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138780</v>
+        <v>129138728</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,26 +3245,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3272,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466057</v>
+        <v>466017</v>
       </c>
       <c r="R26" t="n">
-        <v>6858545</v>
+        <v>6858509</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3316,7 +3325,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3338,7 +3346,7 @@
         <v>129139379</v>
       </c>
       <c r="B27" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139190</v>
+        <v>129138795</v>
       </c>
       <c r="B28" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,21 +3465,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466251</v>
+        <v>466160</v>
       </c>
       <c r="R28" t="n">
-        <v>6858668</v>
+        <v>6858585</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,19 +3525,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138728</v>
+        <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>78797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3568,35 +3566,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3604,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466017</v>
+        <v>466251</v>
       </c>
       <c r="R29" t="n">
-        <v>6858509</v>
+        <v>6858668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,17 +3626,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139263</v>
+        <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>79658</v>
+        <v>78705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465939</v>
+        <v>466175</v>
       </c>
       <c r="R36" t="n">
-        <v>6858553</v>
+        <v>6858646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138827</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465992</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858551</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,9 +4489,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4519,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138758</v>
+        <v>129138933</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>78047</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,21 +4540,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4557,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465994</v>
+        <v>465973</v>
       </c>
       <c r="R38" t="n">
-        <v>6858533</v>
+        <v>6858506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4590,9 +4600,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,10 +4640,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138933</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>78047</v>
+        <v>78796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4631,21 +4651,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4658,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465973</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858506</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,19 +4711,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129139440</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78705</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4742,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466175</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858646</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,19 +4812,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4956,7 +4956,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5072,36 +5072,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>79629</v>
+        <v>92833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5110,10 +5118,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R43" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5183,44 +5191,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>92826</v>
+        <v>79629</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R44" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138835</v>
       </c>
       <c r="B2" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R3" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,9 +847,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,19 +958,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
         <v>129138897</v>
       </c>
       <c r="B5" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129139390</v>
       </c>
       <c r="B8" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,27 +1423,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1451,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R9" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,17 +1488,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,26 +1524,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1556,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R10" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,13 +1590,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129139273</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>79631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1842,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>466112</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,17 +1917,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,26 +1953,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,13 +2029,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B15" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R15" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,9 +2129,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B16" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R16" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,19 +2240,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,7 +2273,7 @@
         <v>129138762</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>129138892</v>
       </c>
       <c r="B18" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129138770</v>
+        <v>129139355</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,26 +2483,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2510,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466025</v>
+        <v>466051</v>
       </c>
       <c r="R19" t="n">
-        <v>6858511</v>
+        <v>6858500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,18 +2544,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2573,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,27 +2599,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2612,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,32 +2659,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129139174</v>
       </c>
       <c r="B23" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139294</v>
+        <v>129139190</v>
       </c>
       <c r="B24" t="n">
-        <v>83005</v>
+        <v>78799</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466066</v>
+        <v>466251</v>
       </c>
       <c r="R24" t="n">
-        <v>6858495</v>
+        <v>6858668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138780</v>
+        <v>129139294</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>83007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466057</v>
+        <v>466066</v>
       </c>
       <c r="R25" t="n">
-        <v>6858545</v>
+        <v>6858495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,9 +3204,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138728</v>
+        <v>129138795</v>
       </c>
       <c r="B26" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,35 +3255,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3281,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466017</v>
+        <v>466160</v>
       </c>
       <c r="R26" t="n">
-        <v>6858509</v>
+        <v>6858585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,6 +3326,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139379</v>
+        <v>129138780</v>
       </c>
       <c r="B27" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3381,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466047</v>
+        <v>466057</v>
       </c>
       <c r="R27" t="n">
-        <v>6858491</v>
+        <v>6858545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3414,19 +3416,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138795</v>
+        <v>129139379</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466160</v>
+        <v>466047</v>
       </c>
       <c r="R28" t="n">
-        <v>6858585</v>
+        <v>6858491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,9 +3517,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,10 +3557,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139190</v>
+        <v>129138728</v>
       </c>
       <c r="B29" t="n">
-        <v>78797</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,26 +3568,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3593,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466251</v>
+        <v>466017</v>
       </c>
       <c r="R29" t="n">
-        <v>6858668</v>
+        <v>6858509</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,28 +3637,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>129138773</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129139434</v>
       </c>
       <c r="B34" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129138812</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139440</v>
+        <v>129139263</v>
       </c>
       <c r="B36" t="n">
-        <v>78705</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466175</v>
+        <v>465939</v>
       </c>
       <c r="R36" t="n">
-        <v>6858646</v>
+        <v>6858553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B37" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,19 +4489,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4529,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B38" t="n">
-        <v>78047</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4540,21 +4530,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R38" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,19 +4590,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4640,10 +4620,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B39" t="n">
-        <v>78796</v>
+        <v>78049</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,21 +4631,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4678,10 +4658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,9 +4691,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>78707</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,9 +4802,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,7 +4845,7 @@
         <v>129175846</v>
       </c>
       <c r="B41" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>129175796</v>
       </c>
       <c r="B45" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>129197630</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>129197620</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>129281326</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>129281312</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129281320</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>129281308</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>129281315</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>129281346</v>
       </c>
       <c r="B54" t="n">
-        <v>79118</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R3" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,19 +847,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R4" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,9 +948,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B11" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,26 +1630,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,13 +1706,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>83007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,9 +1806,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139273</v>
+        <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466112</v>
+        <v>465965</v>
       </c>
       <c r="R13" t="n">
-        <v>6858564</v>
+        <v>6858521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,19 +1917,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139344</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,27 +1958,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466039</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858515</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,17 +2033,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B15" t="n">
         <v>78799</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R15" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,19 +2129,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B16" t="n">
         <v>78799</v>
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R16" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,9 +2230,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,27 +2483,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2511,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R19" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,32 +2543,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2588,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129138770</v>
+        <v>129139355</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,26 +2584,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466025</v>
+        <v>466051</v>
       </c>
       <c r="R20" t="n">
-        <v>6858511</v>
+        <v>6858500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,18 +2645,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>78799</v>
+        <v>91560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R24" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139294</v>
+        <v>129138795</v>
       </c>
       <c r="B25" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466066</v>
+        <v>466160</v>
       </c>
       <c r="R25" t="n">
-        <v>6858495</v>
+        <v>6858585</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,19 +3204,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3244,7 +3234,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138795</v>
+        <v>129138780</v>
       </c>
       <c r="B26" t="n">
         <v>79041</v>
@@ -3282,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466160</v>
+        <v>466057</v>
       </c>
       <c r="R26" t="n">
-        <v>6858585</v>
+        <v>6858545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138780</v>
+        <v>129139294</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466057</v>
+        <v>466066</v>
       </c>
       <c r="R27" t="n">
-        <v>6858545</v>
+        <v>6858495</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,9 +3406,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>78799</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R28" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139263</v>
+        <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465939</v>
+        <v>466175</v>
       </c>
       <c r="R36" t="n">
-        <v>6858553</v>
+        <v>6858646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138827</v>
+        <v>129138758</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465992</v>
+        <v>465994</v>
       </c>
       <c r="R37" t="n">
-        <v>6858551</v>
+        <v>6858533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138758</v>
+        <v>129139263</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,21 +4530,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465994</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>6858533</v>
+        <v>6858553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4590,9 +4590,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4731,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129139440</v>
+        <v>129138827</v>
       </c>
       <c r="B40" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4742,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466175</v>
+        <v>465992</v>
       </c>
       <c r="R40" t="n">
-        <v>6858646</v>
+        <v>6858551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,19 +4812,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>83007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,27 +1630,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1658,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R11" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,17 +1705,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>83007</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,19 +1801,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129138903</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1884,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465965</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858521</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,18 +1903,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139440</v>
+        <v>129138758</v>
       </c>
       <c r="B36" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466175</v>
+        <v>465994</v>
       </c>
       <c r="R36" t="n">
-        <v>6858646</v>
+        <v>6858533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,19 +4378,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,10 +4408,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138758</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4446,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465994</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858533</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,9 +4479,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129139263</v>
+        <v>129138933</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>78049</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,21 +4530,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465939</v>
+        <v>465973</v>
       </c>
       <c r="R38" t="n">
-        <v>6858553</v>
+        <v>6858506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138933</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>78049</v>
+        <v>78798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4641,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465973</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858506</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,19 +4701,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138827</v>
+        <v>129139440</v>
       </c>
       <c r="B40" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465992</v>
+        <v>466175</v>
       </c>
       <c r="R40" t="n">
-        <v>6858551</v>
+        <v>6858646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,9 +4802,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R3" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,9 +847,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,19 +958,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B6" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R6" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,19 +1160,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R7" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,9 +1261,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,26 +1423,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1450,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R9" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,13 +1489,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,27 +1529,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1552,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R10" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,17 +1594,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B15" t="n">
         <v>78799</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R15" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,9 +2129,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B16" t="n">
         <v>78799</v>
@@ -2197,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R16" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,19 +2240,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B24" t="n">
-        <v>91560</v>
+        <v>78799</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R24" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138795</v>
+        <v>129139379</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466160</v>
+        <v>466047</v>
       </c>
       <c r="R25" t="n">
-        <v>6858585</v>
+        <v>6858491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,9 +3204,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138780</v>
+        <v>129139294</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,21 +3255,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3272,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466057</v>
+        <v>466066</v>
       </c>
       <c r="R26" t="n">
-        <v>6858545</v>
+        <v>6858495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,9 +3315,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139294</v>
+        <v>129138795</v>
       </c>
       <c r="B27" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466066</v>
+        <v>466160</v>
       </c>
       <c r="R27" t="n">
-        <v>6858495</v>
+        <v>6858585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,19 +3426,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139190</v>
+        <v>129138780</v>
       </c>
       <c r="B28" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3494,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466251</v>
+        <v>466057</v>
       </c>
       <c r="R28" t="n">
-        <v>6858668</v>
+        <v>6858545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,19 +3527,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,26 +3778,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3805,10 +3806,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R31" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,18 +3839,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3868,10 +3883,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3906,10 +3921,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R32" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,19 +3954,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3979,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,27 +3995,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4018,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R33" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,17 +4070,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R36" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,9 +4378,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4408,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4446,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,19 +4489,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B38" t="n">
-        <v>78049</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,21 +4530,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R38" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4590,19 +4590,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4630,10 +4620,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129139263</v>
       </c>
       <c r="B39" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4631,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465939</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858553</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,9 +4691,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129139440</v>
+        <v>129138933</v>
       </c>
       <c r="B40" t="n">
-        <v>78707</v>
+        <v>78049</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4742,21 +4742,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466175</v>
+        <v>465973</v>
       </c>
       <c r="R40" t="n">
-        <v>6858646</v>
+        <v>6858506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4956,7 +4956,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,6 +6435,103 @@
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129386575</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lill-Svarttjärnen, Lill-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>466175</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6858653</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R3" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,19 +847,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R4" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,9 +948,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,9 +1160,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>78707</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R7" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,19 +1271,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139379</v>
+        <v>129139294</v>
       </c>
       <c r="B25" t="n">
-        <v>91558</v>
+        <v>83007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466047</v>
+        <v>466066</v>
       </c>
       <c r="R25" t="n">
-        <v>6858491</v>
+        <v>6858495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139294</v>
+        <v>129139379</v>
       </c>
       <c r="B26" t="n">
-        <v>83007</v>
+        <v>91560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,23 +3255,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -3282,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466066</v>
+        <v>466047</v>
       </c>
       <c r="R26" t="n">
-        <v>6858495</v>
+        <v>6858491</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3767,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,27 +3774,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3806,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R31" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,17 +3849,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3883,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,26 +3885,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3921,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R32" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,18 +3946,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3984,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R33" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4055,19 +4061,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139440</v>
+        <v>129139263</v>
       </c>
       <c r="B36" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4341,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466175</v>
+        <v>465939</v>
       </c>
       <c r="R36" t="n">
-        <v>6858646</v>
+        <v>6858553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>78049</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R37" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,9 +4485,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4519,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4557,10 +4563,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R38" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4590,9 +4596,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4631,21 +4647,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4658,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,19 +4707,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78049</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4742,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,19 +4808,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4956,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5075,7 +5071,7 @@
         <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,27 +1423,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1451,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R9" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,17 +1488,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,26 +1524,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1556,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R10" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,13 +1590,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>78799</v>
+        <v>91560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,23 +3033,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3060,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R24" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3244,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139379</v>
+        <v>129138795</v>
       </c>
       <c r="B26" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,19 +3251,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466047</v>
+        <v>466160</v>
       </c>
       <c r="R26" t="n">
-        <v>6858491</v>
+        <v>6858585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,19 +3311,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,7 +3341,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138795</v>
+        <v>129138780</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3389,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466160</v>
+        <v>466057</v>
       </c>
       <c r="R27" t="n">
-        <v>6858585</v>
+        <v>6858545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138780</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,26 +3453,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3490,10 +3489,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466057</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858545</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3533,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3551,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138728</v>
+        <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>78799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3564,35 +3562,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3600,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466017</v>
+        <v>466251</v>
       </c>
       <c r="R29" t="n">
-        <v>6858509</v>
+        <v>6858668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,17 +3622,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139271</v>
+        <v>129139365</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,26 +3774,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3801,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466112</v>
+        <v>466352</v>
       </c>
       <c r="R31" t="n">
-        <v>6858564</v>
+        <v>6858689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3849,13 +3850,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3874,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139365</v>
+        <v>129138822</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,27 +3890,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3913,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466352</v>
+        <v>466193</v>
       </c>
       <c r="R32" t="n">
-        <v>6858689</v>
+        <v>6858649</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,32 +3950,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3990,10 +3980,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,21 +3991,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4028,10 +4018,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R33" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,9 +4051,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139263</v>
+        <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465939</v>
+        <v>466175</v>
       </c>
       <c r="R36" t="n">
-        <v>6858553</v>
+        <v>6858646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138933</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>78049</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465973</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858506</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129139440</v>
+        <v>129138933</v>
       </c>
       <c r="B38" t="n">
-        <v>78707</v>
+        <v>78049</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466175</v>
+        <v>465973</v>
       </c>
       <c r="R38" t="n">
-        <v>6858646</v>
+        <v>6858506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138835</v>
       </c>
       <c r="B2" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129138897</v>
       </c>
       <c r="B5" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B6" t="n">
-        <v>78707</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R6" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,19 +1160,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>78709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R7" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,9 +1261,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>129139390</v>
       </c>
       <c r="B8" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B11" t="n">
-        <v>83007</v>
+        <v>78800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,19 +1690,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139344</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,26 +1731,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1768,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466039</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,18 +1792,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1831,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>83011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1847,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,17 +1922,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>129139202</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129138924</v>
       </c>
       <c r="B16" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>129138762</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>129138892</v>
       </c>
       <c r="B18" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R19" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,9 +2543,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,27 +2594,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2612,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,32 +2654,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2689,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B21" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,26 +2695,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2727,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R21" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,13 +2771,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129139174</v>
       </c>
       <c r="B23" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129139294</v>
       </c>
       <c r="B25" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129138795</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129138780</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>129138773</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,27 +3774,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3802,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R31" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,17 +3849,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3879,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,26 +3885,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3917,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R32" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,18 +3946,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3980,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3991,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4018,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R33" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4051,19 +4061,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,7 +4094,7 @@
         <v>129139434</v>
       </c>
       <c r="B34" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>129138812</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138758</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465994</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,19 +4485,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4515,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138933</v>
+        <v>129139263</v>
       </c>
       <c r="B38" t="n">
-        <v>78049</v>
+        <v>79662</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4526,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4563,10 +4553,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465973</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>6858506</v>
+        <v>6858553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4639,7 +4629,7 @@
         <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4737,10 +4727,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129138933</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78051</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4738,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>465973</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,9 +4798,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4841,7 +4841,7 @@
         <v>129175846</v>
       </c>
       <c r="B41" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>129175796</v>
       </c>
       <c r="B45" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>129197630</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>129197620</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>129281346</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>129386575</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129138903</v>
+        <v>129139273</v>
       </c>
       <c r="B11" t="n">
-        <v>78800</v>
+        <v>79633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465965</v>
+        <v>466112</v>
       </c>
       <c r="R11" t="n">
-        <v>6858521</v>
+        <v>6858564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,9 +1690,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>83011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,27 +1741,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1759,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,17 +1816,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1836,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>83011</v>
+        <v>78800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R13" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,19 +1912,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B14" t="n">
-        <v>79633</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,26 +1953,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,13 +2029,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138835</v>
       </c>
       <c r="B2" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129138897</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,9 +1160,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>78709</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R7" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,19 +1271,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>129139390</v>
       </c>
       <c r="B8" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139273</v>
+        <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>79633</v>
+        <v>83012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466112</v>
+        <v>466064</v>
       </c>
       <c r="R11" t="n">
-        <v>6858564</v>
+        <v>6858495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>83011</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,19 +1801,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129138903</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>78800</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1879,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465965</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858521</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,18 +1903,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1942,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139344</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79634</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,27 +1958,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466039</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858515</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,17 +2033,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>129139202</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129138924</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>129138762</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>129138892</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139156</v>
+        <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466125</v>
+        <v>466025</v>
       </c>
       <c r="R19" t="n">
-        <v>6858565</v>
+        <v>6858511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,19 +2543,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129138770</v>
+        <v>129139355</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,26 +2584,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466025</v>
+        <v>466051</v>
       </c>
       <c r="R20" t="n">
-        <v>6858511</v>
+        <v>6858500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,18 +2645,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139355</v>
+        <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,27 +2700,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2723,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466051</v>
+        <v>466125</v>
       </c>
       <c r="R21" t="n">
-        <v>6858500</v>
+        <v>6858565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,17 +2775,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129139174</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B24" t="n">
-        <v>91563</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,19 +3033,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3056,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R24" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139294</v>
+        <v>129139379</v>
       </c>
       <c r="B25" t="n">
-        <v>83011</v>
+        <v>91565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,23 +3144,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466066</v>
+        <v>466047</v>
       </c>
       <c r="R25" t="n">
-        <v>6858495</v>
+        <v>6858491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138795</v>
+        <v>129139294</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>83012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466160</v>
+        <v>466066</v>
       </c>
       <c r="R26" t="n">
-        <v>6858585</v>
+        <v>6858495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,9 +3311,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138780</v>
+        <v>129138795</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466057</v>
+        <v>466160</v>
       </c>
       <c r="R27" t="n">
-        <v>6858545</v>
+        <v>6858585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129138780</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3453,35 +3463,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3489,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466057</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,6 +3534,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3551,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139190</v>
+        <v>129138728</v>
       </c>
       <c r="B29" t="n">
-        <v>78801</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,26 +3564,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3589,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466251</v>
+        <v>466017</v>
       </c>
       <c r="R29" t="n">
-        <v>6858668</v>
+        <v>6858509</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,28 +3633,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>129138773</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,19 +3834,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,27 +3875,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3913,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R32" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,17 +3950,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3990,10 +3975,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,26 +3986,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4028,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R33" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,18 +4047,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>129139434</v>
       </c>
       <c r="B34" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>129138812</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138758</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465994</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858533</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,9 +4485,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4515,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129139263</v>
+        <v>129138933</v>
       </c>
       <c r="B38" t="n">
-        <v>79662</v>
+        <v>78052</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4553,10 +4563,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465939</v>
+        <v>465973</v>
       </c>
       <c r="R38" t="n">
-        <v>6858553</v>
+        <v>6858506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4629,7 +4639,7 @@
         <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4727,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78051</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4798,19 +4808,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4841,7 +4841,7 @@
         <v>129175846</v>
       </c>
       <c r="B41" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,44 +5068,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B43" t="n">
-        <v>92825</v>
+        <v>79634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5114,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R43" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5187,36 +5179,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B44" t="n">
-        <v>79633</v>
+        <v>92827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R44" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
         <v>129175796</v>
       </c>
       <c r="B45" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>129197630</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>129197620</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>129281346</v>
       </c>
       <c r="B54" t="n">
-        <v>79122</v>
+        <v>79123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>129386575</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129138770</v>
+        <v>129139355</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,26 +2483,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2510,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466025</v>
+        <v>466051</v>
       </c>
       <c r="R19" t="n">
-        <v>6858511</v>
+        <v>6858500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,18 +2544,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2573,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,27 +2599,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2612,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,32 +2659,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139190</v>
+        <v>129139294</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>83012</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466251</v>
+        <v>466066</v>
       </c>
       <c r="R24" t="n">
-        <v>6858668</v>
+        <v>6858495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139379</v>
+        <v>129138795</v>
       </c>
       <c r="B25" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,19 +3144,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -3167,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466047</v>
+        <v>466160</v>
       </c>
       <c r="R25" t="n">
-        <v>6858491</v>
+        <v>6858585</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,19 +3204,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3240,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139294</v>
+        <v>129138780</v>
       </c>
       <c r="B26" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,21 +3245,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466066</v>
+        <v>466057</v>
       </c>
       <c r="R26" t="n">
-        <v>6858495</v>
+        <v>6858545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,19 +3305,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138795</v>
+        <v>129139190</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466160</v>
+        <v>466251</v>
       </c>
       <c r="R27" t="n">
-        <v>6858585</v>
+        <v>6858668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,9 +3406,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138780</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,26 +3457,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3490,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466057</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858545</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3537,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138728</v>
+        <v>129139379</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>91569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3564,35 +3566,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3600,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466017</v>
+        <v>466047</v>
       </c>
       <c r="R29" t="n">
-        <v>6858509</v>
+        <v>6858491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,17 +3622,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R31" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,9 +3834,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139271</v>
+        <v>129139365</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,26 +3885,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3902,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466112</v>
+        <v>466352</v>
       </c>
       <c r="R32" t="n">
-        <v>6858564</v>
+        <v>6858689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,13 +3961,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3975,10 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139365</v>
+        <v>129138822</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,27 +4001,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4014,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466352</v>
+        <v>466193</v>
       </c>
       <c r="R33" t="n">
-        <v>6858689</v>
+        <v>6858649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,32 +4061,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138758</v>
       </c>
       <c r="B37" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465994</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,19 +4485,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4515,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138933</v>
+        <v>129139263</v>
       </c>
       <c r="B38" t="n">
-        <v>78052</v>
+        <v>79663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4526,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4563,10 +4553,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465973</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>6858506</v>
+        <v>6858553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4636,10 +4626,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B39" t="n">
-        <v>78801</v>
+        <v>78052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,21 +4637,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4707,9 +4697,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129138827</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>465992</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4952,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>129175770</v>
       </c>
       <c r="B44" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B6" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R6" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,19 +1160,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R7" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,9 +1261,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B11" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,26 +1630,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,13 +1706,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139273</v>
       </c>
       <c r="B12" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466112</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,9 +1806,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1857,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,17 +1932,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129138903</v>
       </c>
       <c r="B14" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>465965</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,19 +2028,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139355</v>
+        <v>129139156</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,27 +2483,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2511,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466051</v>
+        <v>466125</v>
       </c>
       <c r="R19" t="n">
-        <v>6858500</v>
+        <v>6858565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,17 +2558,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2689,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B21" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,26 +2695,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2727,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R21" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,13 +2771,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139294</v>
+        <v>129139190</v>
       </c>
       <c r="B24" t="n">
-        <v>83012</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466066</v>
+        <v>466251</v>
       </c>
       <c r="R24" t="n">
-        <v>6858495</v>
+        <v>6858668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B27" t="n">
-        <v>78802</v>
+        <v>91570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,23 +3346,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -3373,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R27" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129139294</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>83012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,35 +3453,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3493,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3526,17 +3513,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3555,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139379</v>
+        <v>129138728</v>
       </c>
       <c r="B29" t="n">
-        <v>91569</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,22 +3564,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3589,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466047</v>
+        <v>466017</v>
       </c>
       <c r="R29" t="n">
-        <v>6858491</v>
+        <v>6858509</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,28 +3633,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,19 +3834,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,27 +3875,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3913,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R32" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,17 +3950,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3990,10 +3975,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,26 +3986,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4028,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R33" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,18 +4047,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,36 +5068,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>79634</v>
+        <v>92832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5106,10 +5114,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R43" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5179,44 +5187,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>92831</v>
+        <v>79634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R44" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,9 +1160,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R7" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,19 +1271,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,26 +1423,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1450,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R9" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,13 +1489,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,27 +1529,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1552,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R10" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,17 +1594,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,27 +1630,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1658,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R11" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,32 +1690,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139273</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>79634</v>
+        <v>83012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466112</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858564</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1884,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,13 +1918,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129138903</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465965</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858521</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,9 +2018,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,26 +2483,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2510,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R19" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,13 +2559,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2583,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R20" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,9 +2659,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,27 +2710,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2723,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R21" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,32 +2770,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139190</v>
+        <v>129138780</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466251</v>
+        <v>466057</v>
       </c>
       <c r="R24" t="n">
-        <v>6858668</v>
+        <v>6858545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,19 +3093,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138780</v>
+        <v>129139379</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,23 +3235,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -3272,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466057</v>
+        <v>466047</v>
       </c>
       <c r="R26" t="n">
-        <v>6858545</v>
+        <v>6858491</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,9 +3291,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3331,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139379</v>
+        <v>129139294</v>
       </c>
       <c r="B27" t="n">
-        <v>91570</v>
+        <v>83012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,19 +3342,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466047</v>
+        <v>466066</v>
       </c>
       <c r="R27" t="n">
-        <v>6858491</v>
+        <v>6858495</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139294</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>83012</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3453,26 +3453,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3480,10 +3489,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466066</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858495</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,28 +3522,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3551,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138728</v>
+        <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3564,35 +3562,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3600,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466017</v>
+        <v>466251</v>
       </c>
       <c r="R29" t="n">
-        <v>6858509</v>
+        <v>6858668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,17 +3622,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R31" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,9 +3834,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,21 +3885,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3902,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R32" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,19 +3945,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138758</v>
+        <v>129138933</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465994</v>
+        <v>465973</v>
       </c>
       <c r="R37" t="n">
-        <v>6858533</v>
+        <v>6858506</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,9 +4485,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4626,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138933</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>78052</v>
+        <v>78801</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,21 +4647,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4664,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465973</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858506</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4697,19 +4707,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138827</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465992</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858551</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B12" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,26 +1731,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1758,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R12" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,13 +1807,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1831,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129139273</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1847,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>466112</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,17 +1922,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129139302</v>
       </c>
       <c r="B14" t="n">
-        <v>79634</v>
+        <v>83012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>466064</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858495</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129138780</v>
+        <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,23 +3033,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3060,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466057</v>
+        <v>466047</v>
       </c>
       <c r="R24" t="n">
-        <v>6858545</v>
+        <v>6858491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,9 +3089,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138795</v>
+        <v>129139294</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,21 +3140,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466160</v>
+        <v>466066</v>
       </c>
       <c r="R25" t="n">
-        <v>6858585</v>
+        <v>6858495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,9 +3200,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3224,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139379</v>
+        <v>129138728</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,22 +3251,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3258,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466047</v>
+        <v>466017</v>
       </c>
       <c r="R26" t="n">
-        <v>6858491</v>
+        <v>6858509</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,28 +3320,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3331,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139294</v>
+        <v>129138795</v>
       </c>
       <c r="B27" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3342,21 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3369,10 +3387,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466066</v>
+        <v>466160</v>
       </c>
       <c r="R27" t="n">
-        <v>6858495</v>
+        <v>6858585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,19 +3420,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129138780</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3453,35 +3461,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3489,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466057</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,6 +3532,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R3" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,9 +847,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,19 +958,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129138713</v>
+        <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,27 +1423,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1451,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465932</v>
+        <v>465991</v>
       </c>
       <c r="R9" t="n">
-        <v>6858501</v>
+        <v>6858526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,17 +1488,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1518,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129138755</v>
+        <v>129138713</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,26 +1524,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1556,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465991</v>
+        <v>465932</v>
       </c>
       <c r="R10" t="n">
-        <v>6858526</v>
+        <v>6858501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,13 +1590,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129138903</v>
+        <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>83012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465965</v>
+        <v>466064</v>
       </c>
       <c r="R11" t="n">
-        <v>6858521</v>
+        <v>6858495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,9 +1690,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,27 +1741,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1759,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,32 +1801,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1836,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,13 +1918,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139302</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>83012</v>
+        <v>79634</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466064</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858495</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139156</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466125</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858565</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,19 +2659,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R21" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,9 +2760,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3025,7 +3025,7 @@
         <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138728</v>
+        <v>129138780</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,35 +3251,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3287,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466017</v>
+        <v>466057</v>
       </c>
       <c r="R26" t="n">
-        <v>6858509</v>
+        <v>6858545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3331,6 +3322,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3450,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138780</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,26 +3453,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3488,10 +3489,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466057</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858545</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3533,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B37" t="n">
-        <v>78052</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R37" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,19 +4485,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4636,10 +4626,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B39" t="n">
-        <v>78801</v>
+        <v>78052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,21 +4637,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4707,9 +4697,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129138827</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>465992</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4952,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R3" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,19 +847,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R4" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,9 +948,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129139344</v>
       </c>
       <c r="B11" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,26 +1630,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>466039</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,13 +1706,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>78801</v>
+        <v>83012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,9 +1806,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1857,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,32 +1917,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,27 +2483,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2511,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R19" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,32 +2543,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2588,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R20" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,9 +2644,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2689,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B21" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,26 +2695,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2727,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R21" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,13 +2771,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B24" t="n">
-        <v>91573</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,19 +3033,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3056,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R24" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139294</v>
+        <v>129138728</v>
       </c>
       <c r="B25" t="n">
-        <v>83012</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,26 +3144,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3167,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466066</v>
+        <v>466017</v>
       </c>
       <c r="R25" t="n">
-        <v>6858495</v>
+        <v>6858509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,28 +3213,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3240,7 +3242,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138780</v>
+        <v>129138795</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3278,10 +3280,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466057</v>
+        <v>466160</v>
       </c>
       <c r="R26" t="n">
-        <v>6858545</v>
+        <v>6858585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,7 +3343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138795</v>
+        <v>129138780</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3379,10 +3381,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466160</v>
+        <v>466057</v>
       </c>
       <c r="R27" t="n">
-        <v>6858585</v>
+        <v>6858545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129139294</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>83012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3453,35 +3455,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3489,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,17 +3515,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3551,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,23 +3566,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R29" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4515,10 +4515,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B38" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R38" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,19 +4586,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4737,10 +4727,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138827</v>
+        <v>129139263</v>
       </c>
       <c r="B40" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4738,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465992</v>
+        <v>465939</v>
       </c>
       <c r="R40" t="n">
-        <v>6858551</v>
+        <v>6858553</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,9 +4798,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,44 +5068,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>79634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5114,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R43" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5187,36 +5179,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B44" t="n">
-        <v>79634</v>
+        <v>92835</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R44" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6528,6 +6528,205 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129603389</v>
+      </c>
+      <c r="B56" t="n">
+        <v>82878</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lill-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>466123</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6858493</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129603461</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lill-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>466135</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6858496</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B6" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R6" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,19 +1160,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R7" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,9 +1261,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,27 +1630,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1658,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R11" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,17 +1705,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B12" t="n">
-        <v>83012</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R12" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,19 +1801,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129138903</v>
+        <v>129139344</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,26 +1842,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1884,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465965</v>
+        <v>466039</v>
       </c>
       <c r="R13" t="n">
-        <v>6858521</v>
+        <v>6858515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,18 +1903,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2573,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B20" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,26 +2584,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2611,10 +2612,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R20" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,13 +2660,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139355</v>
+        <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,27 +2700,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2723,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466051</v>
+        <v>466125</v>
       </c>
       <c r="R21" t="n">
-        <v>6858500</v>
+        <v>6858565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,17 +2775,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>91573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,23 +3033,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3060,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R24" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138728</v>
+        <v>129138795</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,35 +3140,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3180,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466017</v>
+        <v>466160</v>
       </c>
       <c r="R25" t="n">
-        <v>6858509</v>
+        <v>6858585</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,6 +3211,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138795</v>
+        <v>129138780</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3280,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466160</v>
+        <v>466057</v>
       </c>
       <c r="R26" t="n">
-        <v>6858585</v>
+        <v>6858545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3343,10 +3331,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138780</v>
+        <v>129139294</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3342,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3381,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466057</v>
+        <v>466066</v>
       </c>
       <c r="R27" t="n">
-        <v>6858545</v>
+        <v>6858495</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3414,9 +3402,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139294</v>
+        <v>129138728</v>
       </c>
       <c r="B28" t="n">
-        <v>83012</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,26 +3453,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3482,10 +3489,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466066</v>
+        <v>466017</v>
       </c>
       <c r="R28" t="n">
-        <v>6858495</v>
+        <v>6858509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,28 +3522,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3555,10 +3551,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,19 +3562,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R29" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,19 +3834,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,21 +3875,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R32" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,9 +3935,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139440</v>
+        <v>129138758</v>
       </c>
       <c r="B36" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466175</v>
+        <v>465994</v>
       </c>
       <c r="R36" t="n">
-        <v>6858646</v>
+        <v>6858533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,19 +4374,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4414,10 +4404,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4415,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4442,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R37" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,9 +4475,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138827</v>
+        <v>129139263</v>
       </c>
       <c r="B38" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465992</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>6858551</v>
+        <v>6858553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,9 +4586,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4727,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B40" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R40" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4798,19 +4808,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,36 +5068,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>79634</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5106,10 +5114,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R43" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5179,44 +5187,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>92835</v>
+        <v>79634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R44" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R3" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,9 +847,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,19 +958,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139344</v>
+        <v>129139273</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,27 +1842,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466039</v>
+        <v>466112</v>
       </c>
       <c r="R13" t="n">
-        <v>6858515</v>
+        <v>6858564</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,17 +1917,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B14" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,26 +1953,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,13 +2029,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R19" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,9 +2543,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139355</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,27 +2594,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2612,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466051</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858500</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,32 +2654,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2689,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139156</v>
+        <v>129139355</v>
       </c>
       <c r="B21" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,26 +2695,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2727,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466125</v>
+        <v>466051</v>
       </c>
       <c r="R21" t="n">
-        <v>6858565</v>
+        <v>6858500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,13 +2771,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139379</v>
+        <v>129138728</v>
       </c>
       <c r="B24" t="n">
-        <v>91573</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,22 +3033,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3056,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466047</v>
+        <v>466017</v>
       </c>
       <c r="R24" t="n">
-        <v>6858491</v>
+        <v>6858509</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,28 +3102,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3129,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129138795</v>
+        <v>129139190</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3167,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466160</v>
+        <v>466251</v>
       </c>
       <c r="R25" t="n">
-        <v>6858585</v>
+        <v>6858668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,9 +3202,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3242,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138780</v>
+        <v>129138795</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3268,10 +3280,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466057</v>
+        <v>466160</v>
       </c>
       <c r="R26" t="n">
-        <v>6858545</v>
+        <v>6858585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3331,10 +3343,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129139294</v>
+        <v>129138780</v>
       </c>
       <c r="B27" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3342,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3369,10 +3381,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466066</v>
+        <v>466057</v>
       </c>
       <c r="R27" t="n">
-        <v>6858495</v>
+        <v>6858545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,19 +3414,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138728</v>
+        <v>129139294</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>83012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3453,35 +3455,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3489,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466017</v>
+        <v>466066</v>
       </c>
       <c r="R28" t="n">
-        <v>6858509</v>
+        <v>6858495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,17 +3515,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3551,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,23 +3566,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R29" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R36" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,9 +4374,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139440</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4415,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4442,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466175</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858646</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B38" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4553,10 +4563,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R38" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,19 +4596,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4626,10 +4626,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B39" t="n">
-        <v>78052</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,21 +4637,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R39" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4697,19 +4697,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,10 +4727,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B40" t="n">
-        <v>78801</v>
+        <v>78052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4738,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R40" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,9 +4798,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6727,6 +6727,208 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129649656</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>465996</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6858543</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129649651</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>465942</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6858506</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129139249</v>
+        <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465971</v>
+        <v>465969</v>
       </c>
       <c r="R3" t="n">
-        <v>6858535</v>
+        <v>6858494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,19 +847,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129138751</v>
+        <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>465971</v>
       </c>
       <c r="R4" t="n">
-        <v>6858494</v>
+        <v>6858535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,9 +948,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129138747</v>
+        <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465928</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>6858495</v>
+        <v>6858561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,9 +1160,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139428</v>
+        <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465928</v>
       </c>
       <c r="R7" t="n">
-        <v>6858561</v>
+        <v>6858495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,19 +1271,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139302</v>
+        <v>129139273</v>
       </c>
       <c r="B11" t="n">
-        <v>83012</v>
+        <v>79634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466064</v>
+        <v>466112</v>
       </c>
       <c r="R11" t="n">
-        <v>6858495</v>
+        <v>6858564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129138903</v>
+        <v>129139344</v>
       </c>
       <c r="B12" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,26 +1741,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1768,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465965</v>
+        <v>466039</v>
       </c>
       <c r="R12" t="n">
-        <v>6858521</v>
+        <v>6858515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,18 +1802,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1831,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139273</v>
+        <v>129139302</v>
       </c>
       <c r="B13" t="n">
-        <v>79634</v>
+        <v>83012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466112</v>
+        <v>466064</v>
       </c>
       <c r="R13" t="n">
-        <v>6858564</v>
+        <v>6858495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139344</v>
+        <v>129138903</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,27 +1968,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466039</v>
+        <v>465965</v>
       </c>
       <c r="R14" t="n">
-        <v>6858515</v>
+        <v>6858521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,32 +2028,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129138728</v>
+        <v>129139190</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,35 +3033,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3069,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466017</v>
+        <v>466251</v>
       </c>
       <c r="R24" t="n">
-        <v>6858509</v>
+        <v>6858668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,17 +3093,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3131,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139190</v>
+        <v>129139379</v>
       </c>
       <c r="B25" t="n">
-        <v>78802</v>
+        <v>91573</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,23 +3144,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -3169,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466251</v>
+        <v>466047</v>
       </c>
       <c r="R25" t="n">
-        <v>6858668</v>
+        <v>6858491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129138795</v>
+        <v>129139294</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3280,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466160</v>
+        <v>466066</v>
       </c>
       <c r="R26" t="n">
-        <v>6858585</v>
+        <v>6858495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,9 +3311,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,7 +3351,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138780</v>
+        <v>129138795</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3381,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466057</v>
+        <v>466160</v>
       </c>
       <c r="R27" t="n">
-        <v>6858545</v>
+        <v>6858585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129139294</v>
+        <v>129138780</v>
       </c>
       <c r="B28" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466066</v>
+        <v>466057</v>
       </c>
       <c r="R28" t="n">
-        <v>6858495</v>
+        <v>6858545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,19 +3523,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139379</v>
+        <v>129138728</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,22 +3564,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3589,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466047</v>
+        <v>466017</v>
       </c>
       <c r="R29" t="n">
-        <v>6858491</v>
+        <v>6858509</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,28 +3633,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129138822</v>
+        <v>129139365</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,26 +3774,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3801,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466352</v>
       </c>
       <c r="R31" t="n">
-        <v>6858649</v>
+        <v>6858689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,18 +3835,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3864,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129139271</v>
+        <v>129138822</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,21 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3902,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466112</v>
+        <v>466193</v>
       </c>
       <c r="R32" t="n">
-        <v>6858564</v>
+        <v>6858649</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,19 +3950,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3975,10 +3980,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139365</v>
+        <v>129139271</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,27 +3991,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4014,10 +4018,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466352</v>
+        <v>466112</v>
       </c>
       <c r="R33" t="n">
-        <v>6858689</v>
+        <v>6858564</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,17 +4066,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B37" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,19 +4485,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4515,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138827</v>
+        <v>129138758</v>
       </c>
       <c r="B38" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4526,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4563,10 +4553,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465992</v>
+        <v>465994</v>
       </c>
       <c r="R38" t="n">
-        <v>6858551</v>
+        <v>6858533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4626,10 +4616,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138758</v>
+        <v>129139263</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,21 +4627,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465994</v>
+        <v>465939</v>
       </c>
       <c r="R39" t="n">
-        <v>6858533</v>
+        <v>6858553</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4697,9 +4687,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B11" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,26 +1630,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R11" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,13 +1706,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139344</v>
+        <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,27 +1746,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1769,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466039</v>
+        <v>466064</v>
       </c>
       <c r="R12" t="n">
-        <v>6858515</v>
+        <v>6858495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,17 +1821,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139302</v>
+        <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>83012</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466064</v>
+        <v>465965</v>
       </c>
       <c r="R13" t="n">
-        <v>6858495</v>
+        <v>6858521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,19 +1917,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129138903</v>
+        <v>129139273</v>
       </c>
       <c r="B14" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465965</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858521</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,9 +2018,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129139156</v>
+        <v>129138770</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466125</v>
+        <v>466025</v>
       </c>
       <c r="R19" t="n">
-        <v>6858565</v>
+        <v>6858511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,19 +2543,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129138770</v>
+        <v>129139156</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466025</v>
+        <v>466125</v>
       </c>
       <c r="R20" t="n">
-        <v>6858511</v>
+        <v>6858565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,9 +2644,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129139190</v>
+        <v>129138728</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,26 +3033,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3060,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466251</v>
+        <v>466017</v>
       </c>
       <c r="R24" t="n">
-        <v>6858668</v>
+        <v>6858509</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,28 +3102,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3133,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139379</v>
+        <v>129139190</v>
       </c>
       <c r="B25" t="n">
-        <v>91573</v>
+        <v>78802</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,19 +3142,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -3167,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466047</v>
+        <v>466251</v>
       </c>
       <c r="R25" t="n">
-        <v>6858491</v>
+        <v>6858668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3553,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138728</v>
+        <v>129139379</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3564,35 +3566,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3600,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466017</v>
+        <v>466047</v>
       </c>
       <c r="R29" t="n">
-        <v>6858509</v>
+        <v>6858491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,17 +3622,28 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129139365</v>
+        <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,27 +3774,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3802,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466352</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>6858689</v>
+        <v>6858649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,32 +3834,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3879,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129138822</v>
+        <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,21 +3875,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3917,10 +3902,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466193</v>
+        <v>466112</v>
       </c>
       <c r="R32" t="n">
-        <v>6858649</v>
+        <v>6858564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,9 +3935,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3980,10 +3975,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129139271</v>
+        <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3991,26 +3986,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4018,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466112</v>
+        <v>466352</v>
       </c>
       <c r="R33" t="n">
-        <v>6858564</v>
+        <v>6858689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,13 +4062,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129138827</v>
+        <v>129139263</v>
       </c>
       <c r="B37" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465992</v>
+        <v>465939</v>
       </c>
       <c r="R37" t="n">
-        <v>6858551</v>
+        <v>6858553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,9 +4485,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4515,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138758</v>
+        <v>129138933</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>78052</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,21 +4536,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4553,10 +4563,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465994</v>
+        <v>465973</v>
       </c>
       <c r="R38" t="n">
-        <v>6858533</v>
+        <v>6858506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,9 +4596,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4616,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B39" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4627,21 +4647,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4654,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R39" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4687,19 +4707,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4727,10 +4737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138933</v>
+        <v>129138758</v>
       </c>
       <c r="B40" t="n">
-        <v>78052</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,21 +4748,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465973</v>
+        <v>465994</v>
       </c>
       <c r="R40" t="n">
-        <v>6858506</v>
+        <v>6858533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4798,19 +4808,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,44 +5068,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>79634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5114,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R43" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5187,36 +5179,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B44" t="n">
-        <v>79634</v>
+        <v>92835</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R44" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138835</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129138751</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129139249</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>129138897</v>
       </c>
       <c r="B5" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129139428</v>
       </c>
       <c r="B6" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129138747</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>129139390</v>
       </c>
       <c r="B8" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>129138755</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>129138713</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129139344</v>
+        <v>129139273</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,27 +1630,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1658,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466039</v>
+        <v>466112</v>
       </c>
       <c r="R11" t="n">
-        <v>6858515</v>
+        <v>6858564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,17 +1705,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1738,7 +1733,7 @@
         <v>129139302</v>
       </c>
       <c r="B12" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1844,7 @@
         <v>129138903</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139273</v>
+        <v>129139344</v>
       </c>
       <c r="B14" t="n">
-        <v>79634</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,26 +1953,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1985,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466112</v>
+        <v>466039</v>
       </c>
       <c r="R14" t="n">
-        <v>6858564</v>
+        <v>6858515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,13 +2029,17 @@
           <t>21:54</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129139202</v>
+        <v>129138924</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466030</v>
+        <v>465973</v>
       </c>
       <c r="R15" t="n">
-        <v>6858650</v>
+        <v>6858506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,19 +2129,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129138924</v>
+        <v>129139202</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465973</v>
+        <v>466030</v>
       </c>
       <c r="R16" t="n">
-        <v>6858506</v>
+        <v>6858650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,9 +2230,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,7 +2273,7 @@
         <v>129138762</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>129138892</v>
       </c>
       <c r="B18" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129138770</v>
+        <v>129139355</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,26 +2483,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2510,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466025</v>
+        <v>466051</v>
       </c>
       <c r="R19" t="n">
-        <v>6858511</v>
+        <v>6858500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,18 +2544,32 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2573,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129139156</v>
+        <v>129138770</v>
       </c>
       <c r="B20" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466125</v>
+        <v>466025</v>
       </c>
       <c r="R20" t="n">
-        <v>6858565</v>
+        <v>6858511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,19 +2659,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129139355</v>
+        <v>129139156</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>78828</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,27 +2700,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2723,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466051</v>
+        <v>466125</v>
       </c>
       <c r="R21" t="n">
-        <v>6858500</v>
+        <v>6858565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,17 +2775,13 @@
           <t>21:54</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>129139291</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129139174</v>
       </c>
       <c r="B23" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129138728</v>
+        <v>129138780</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,35 +3033,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3069,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466017</v>
+        <v>466057</v>
       </c>
       <c r="R24" t="n">
-        <v>6858509</v>
+        <v>6858545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,6 +3104,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3131,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129139190</v>
+        <v>129139294</v>
       </c>
       <c r="B25" t="n">
-        <v>78802</v>
+        <v>83039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466251</v>
+        <v>466066</v>
       </c>
       <c r="R25" t="n">
-        <v>6858668</v>
+        <v>6858495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129139294</v>
+        <v>129138795</v>
       </c>
       <c r="B26" t="n">
-        <v>83012</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,21 +3245,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3280,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466066</v>
+        <v>466160</v>
       </c>
       <c r="R26" t="n">
-        <v>6858495</v>
+        <v>6858585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,19 +3305,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129138795</v>
+        <v>129139190</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466160</v>
+        <v>466251</v>
       </c>
       <c r="R27" t="n">
-        <v>6858585</v>
+        <v>6858668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,9 +3406,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129138780</v>
+        <v>129139379</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,23 +3457,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -3492,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466057</v>
+        <v>466047</v>
       </c>
       <c r="R28" t="n">
-        <v>6858545</v>
+        <v>6858491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,9 +3513,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129139379</v>
+        <v>129138728</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>57890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,22 +3564,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3589,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466047</v>
+        <v>466017</v>
       </c>
       <c r="R29" t="n">
-        <v>6858491</v>
+        <v>6858509</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,28 +3633,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>129138773</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>129138822</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>129139271</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>129139365</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>129139434</v>
       </c>
       <c r="B34" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>129138812</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129139440</v>
+        <v>129138758</v>
       </c>
       <c r="B36" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466175</v>
+        <v>465994</v>
       </c>
       <c r="R36" t="n">
-        <v>6858646</v>
+        <v>6858533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,19 +4374,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4414,10 +4404,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129139263</v>
+        <v>129138827</v>
       </c>
       <c r="B37" t="n">
-        <v>79663</v>
+        <v>78827</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,21 +4415,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4442,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465939</v>
+        <v>465992</v>
       </c>
       <c r="R37" t="n">
-        <v>6858553</v>
+        <v>6858551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,19 +4475,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4525,10 +4505,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129138933</v>
+        <v>129139263</v>
       </c>
       <c r="B38" t="n">
-        <v>78052</v>
+        <v>79689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,21 +4516,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4563,10 +4543,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465973</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>6858506</v>
+        <v>6858553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4636,10 +4616,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129138827</v>
+        <v>129138933</v>
       </c>
       <c r="B39" t="n">
-        <v>78801</v>
+        <v>78078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,21 +4627,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465992</v>
+        <v>465973</v>
       </c>
       <c r="R39" t="n">
-        <v>6858551</v>
+        <v>6858506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4707,9 +4687,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,10 +4727,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129138758</v>
+        <v>129139440</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,21 +4738,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465994</v>
+        <v>466175</v>
       </c>
       <c r="R40" t="n">
-        <v>6858533</v>
+        <v>6858646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,9 +4798,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4841,7 +4841,7 @@
         <v>129175846</v>
       </c>
       <c r="B41" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>129175788</v>
       </c>
       <c r="B42" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5068,36 +5068,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175800</v>
+        <v>129175770</v>
       </c>
       <c r="B43" t="n">
-        <v>79634</v>
+        <v>92863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5106,10 +5114,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466330</v>
+        <v>466134</v>
       </c>
       <c r="R43" t="n">
-        <v>6858715</v>
+        <v>6858579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5179,44 +5187,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175770</v>
+        <v>129175800</v>
       </c>
       <c r="B44" t="n">
-        <v>92835</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466134</v>
+        <v>466330</v>
       </c>
       <c r="R44" t="n">
-        <v>6858579</v>
+        <v>6858715</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
         <v>129175796</v>
       </c>
       <c r="B45" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>129197630</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>129197620</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>129281326</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>129281312</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>129281320</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129281308</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>129281315</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>129281346</v>
       </c>
       <c r="B54" t="n">
-        <v>79123</v>
+        <v>79149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>129386575</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>129603461</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5634,7 +5634,7 @@
         <v>129281326</v>
       </c>
       <c r="B48" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>129281312</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>129281320</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129281308</v>
       </c>
       <c r="B51" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>129281315</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>129281346</v>
       </c>
       <c r="B54" t="n">
-        <v>79149</v>
+        <v>79154</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>129386575</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>129603461</v>
       </c>
       <c r="B57" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6929,6 +6929,107 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129758138</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56916</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storsvarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>465990</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6858565</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -5634,7 +5634,7 @@
         <v>129281326</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>129281312</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>129281320</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129281308</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129281353</v>
       </c>
       <c r="B52" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>129281315</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>129281346</v>
       </c>
       <c r="B54" t="n">
-        <v>79154</v>
+        <v>79155</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>129386575</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>129603461</v>
       </c>
       <c r="B57" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129758138</v>
       </c>
       <c r="B60" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -6436,7 +6436,7 @@
         <v>129386575</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -6934,7 +6934,7 @@
         <v>129758138</v>
       </c>
       <c r="B60" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>129603461</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -6533,7 +6533,7 @@
         <v>129603389</v>
       </c>
       <c r="B56" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>129603461</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129758138</v>
       </c>
       <c r="B60" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -6732,7 +6732,7 @@
         <v>129649656</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129649651</v>
       </c>
       <c r="B59" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129138835</v>
+        <v>129139390</v>
       </c>
       <c r="B2" t="n">
-        <v>78827</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466167</v>
+        <v>466239</v>
       </c>
       <c r="R2" t="n">
-        <v>6858595</v>
+        <v>6858650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,9 +746,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +789,7 @@
         <v>129139428</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139390</v>
+        <v>129139434</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466239</v>
+        <v>466149</v>
       </c>
       <c r="R4" t="n">
-        <v>6858650</v>
+        <v>6858600</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129139273</v>
+        <v>129139440</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466112</v>
+        <v>466175</v>
       </c>
       <c r="R5" t="n">
-        <v>6858564</v>
+        <v>6858646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139202</v>
+        <v>129175770</v>
       </c>
       <c r="B6" t="n">
-        <v>78828</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,25 +1130,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1147,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466030</v>
+        <v>466134</v>
       </c>
       <c r="R6" t="n">
-        <v>6858650</v>
+        <v>6858579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,22 +1195,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139156</v>
+        <v>129175788</v>
       </c>
       <c r="B7" t="n">
-        <v>78828</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,25 +1249,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1258,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466125</v>
+        <v>466189</v>
       </c>
       <c r="R7" t="n">
-        <v>6858565</v>
+        <v>6858646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,22 +1314,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,32 +1357,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139174</v>
+        <v>129138780</v>
       </c>
       <c r="B8" t="n">
-        <v>78828</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466149</v>
+        <v>466057</v>
       </c>
       <c r="R8" t="n">
-        <v>6858653</v>
+        <v>6858545</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,19 +1428,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,11 +1461,11 @@
         <v>129138795</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1543,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129139190</v>
+        <v>129138812</v>
       </c>
       <c r="B10" t="n">
-        <v>78828</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466251</v>
+        <v>466130</v>
       </c>
       <c r="R10" t="n">
-        <v>6858668</v>
+        <v>6858644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,19 +1630,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>21:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,11 +1663,11 @@
         <v>129138822</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1755,48 +1761,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129139271</v>
+        <v>129386575</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Lill-Svarttjärnen, Lill-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466112</v>
+        <v>466175</v>
       </c>
       <c r="R12" t="n">
-        <v>6858564</v>
+        <v>6858653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,22 +1826,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,29 +1840,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129139365</v>
+        <v>129138835</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,27 +1869,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1905,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466352</v>
+        <v>466167</v>
       </c>
       <c r="R13" t="n">
-        <v>6858689</v>
+        <v>6858595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,32 +1929,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>21:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1982,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129139434</v>
+        <v>129139271</v>
       </c>
       <c r="B14" t="n">
-        <v>78736</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466149</v>
+        <v>466112</v>
       </c>
       <c r="R14" t="n">
-        <v>6858600</v>
+        <v>6858564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129138812</v>
+        <v>129281312</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,26 +2081,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2131,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466130</v>
+        <v>466110</v>
       </c>
       <c r="R15" t="n">
-        <v>6858644</v>
+        <v>6858566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,12 +2139,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,7 +2168,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2194,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129139440</v>
+        <v>129281315</v>
       </c>
       <c r="B16" t="n">
-        <v>78736</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,26 +2197,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2232,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466175</v>
+        <v>466103</v>
       </c>
       <c r="R16" t="n">
-        <v>6858646</v>
+        <v>6858666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,22 +2255,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,7 +2284,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2305,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129175846</v>
+        <v>129281320</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,26 +2313,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2343,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466288</v>
+        <v>466268</v>
       </c>
       <c r="R17" t="n">
-        <v>6858746</v>
+        <v>6858643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2371,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2383,7 +2381,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2391,13 +2389,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2416,44 +2418,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175788</v>
+        <v>129139156</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2462,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466189</v>
+        <v>466125</v>
       </c>
       <c r="R18" t="n">
-        <v>6858646</v>
+        <v>6858565</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,22 +2486,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,44 +2529,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175770</v>
+        <v>129139174</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2581,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466134</v>
+        <v>466149</v>
       </c>
       <c r="R19" t="n">
-        <v>6858579</v>
+        <v>6858653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,22 +2597,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,10 +2640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175800</v>
+        <v>129139190</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,21 +2651,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466330</v>
+        <v>466251</v>
       </c>
       <c r="R20" t="n">
-        <v>6858715</v>
+        <v>6858668</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,22 +2708,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175796</v>
+        <v>129139202</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,21 +2762,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2803,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466166</v>
+        <v>466030</v>
       </c>
       <c r="R21" t="n">
-        <v>6858663</v>
+        <v>6858650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,22 +2819,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129197630</v>
+        <v>129139273</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2887,21 +2873,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2914,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466314</v>
+        <v>466112</v>
       </c>
       <c r="R22" t="n">
-        <v>6858740</v>
+        <v>6858564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,22 +2930,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,10 +2973,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129197620</v>
+        <v>129175796</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2998,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3025,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466329</v>
+        <v>466166</v>
       </c>
       <c r="R23" t="n">
-        <v>6858717</v>
+        <v>6858663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3055,22 +3041,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,10 +3084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129281326</v>
+        <v>129175846</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>79917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,27 +3095,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3137,10 +3122,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466342</v>
+        <v>466288</v>
       </c>
       <c r="R24" t="n">
-        <v>6858743</v>
+        <v>6858746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3167,7 +3152,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3177,7 +3162,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3185,17 +3170,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3214,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129281312</v>
+        <v>129281353</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>90932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3225,27 +3206,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3253,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466110</v>
+        <v>466390</v>
       </c>
       <c r="R25" t="n">
-        <v>6858566</v>
+        <v>6858754</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,17 +3281,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack tall.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3330,38 +3306,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129281320</v>
+        <v>129197620</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3369,10 +3344,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466268</v>
+        <v>466329</v>
       </c>
       <c r="R26" t="n">
-        <v>6858643</v>
+        <v>6858717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,27 +3374,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack tall.</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3428,6 +3398,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3446,32 +3417,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129281353</v>
+        <v>129197630</v>
       </c>
       <c r="B27" t="n">
-        <v>90620</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3484,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466390</v>
+        <v>466314</v>
       </c>
       <c r="R27" t="n">
-        <v>6858754</v>
+        <v>6858740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,22 +3485,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129281315</v>
+        <v>129139365</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,10 +3567,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466103</v>
+        <v>466352</v>
       </c>
       <c r="R28" t="n">
-        <v>6858666</v>
+        <v>6858689</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,27 +3597,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3673,10 +3644,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129386575</v>
+        <v>129281326</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,34 +3655,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Svarttjärnen, Lill-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466175</v>
+        <v>466342</v>
       </c>
       <c r="R29" t="n">
-        <v>6858653</v>
+        <v>6858743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,12 +3713,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3758,15 +3748,126 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129175800</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>466330</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6858715</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43579-2025 artfynd.xlsx
+++ b/artfynd/A 43579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139428</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139434</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139440</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281353</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175770</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175788</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138780</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138795</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1980,6 +2040,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197620</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197630</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386575</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2289,6 +2364,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138835</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2400,6 +2480,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139271</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,6 +2601,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139365</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281312</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2748,6 +2843,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281315</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2864,6 +2964,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281320</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2980,6 +3085,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281326</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3091,6 +3201,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139156</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139174</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3313,6 +3433,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139190</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3424,6 +3549,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139202</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3535,6 +3665,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139273</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3646,6 +3781,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175796</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3757,6 +3897,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175800</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3868,8 +4013,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175846</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>